--- a/data/Oficina_de_procuradora_de_mujeres/opmMedio.xlsx
+++ b/data/Oficina_de_procuradora_de_mujeres/opmMedio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Oficina_de_procuradora_de_mujeres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54207649-C074-4A93-8077-0E1541FF4159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7594442B-7C54-4078-8EBB-05A78EAA336F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -80,7 +80,7 @@
     <t>Personas atendidas (enero - diciembre 2025)</t>
   </si>
   <si>
-    <t>Personas atendidas (enero - abril 2026)</t>
+    <t>Personas atendidas (enero - julio 2026)</t>
   </si>
 </sst>
 </file>
@@ -127,12 +127,27 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -145,7 +160,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -157,6 +171,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -388,33 +405,33 @@
     <col min="9" max="26" width="10.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+    <row r="1" spans="1:8" ht="55.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>6</v>
       </c>
@@ -436,11 +453,11 @@
       <c r="G2" s="2">
         <v>2752</v>
       </c>
-      <c r="H2">
-        <v>738</v>
+      <c r="H2" s="8">
+        <v>1447</v>
       </c>
     </row>
-    <row r="3" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>7</v>
       </c>
@@ -462,11 +479,11 @@
       <c r="G3" s="1">
         <v>2</v>
       </c>
-      <c r="H3">
-        <v>1</v>
+      <c r="H3" s="8">
+        <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>8</v>
       </c>
@@ -488,21 +505,21 @@
       <c r="G4" s="1">
         <v>255</v>
       </c>
-      <c r="H4">
-        <v>30</v>
+      <c r="H4" s="8">
+        <v>123</v>
       </c>
     </row>
-    <row r="5" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>10</v>
       </c>
       <c r="E5" s="1">
@@ -514,35 +531,41 @@
       <c r="G5" s="1">
         <v>654</v>
       </c>
-      <c r="H5">
-        <v>148</v>
+      <c r="H5" s="8">
+        <v>397</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6">
+        <f t="shared" ref="B6:G6" si="0">SUM(B2:B5)</f>
         <v>3060</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6">
+        <f t="shared" si="0"/>
         <v>3841</v>
       </c>
-      <c r="D6" s="4">
-        <f>SUM(D2:D4)</f>
+      <c r="D6">
+        <f t="shared" si="0"/>
         <v>3613</v>
       </c>
       <c r="E6">
+        <f t="shared" si="0"/>
         <v>2885</v>
       </c>
-      <c r="F6" s="1">
+      <c r="F6">
+        <f t="shared" si="0"/>
         <v>3703</v>
       </c>
-      <c r="G6" s="2">
+      <c r="G6">
+        <f t="shared" si="0"/>
         <v>3663</v>
       </c>
       <c r="H6">
-        <v>917</v>
+        <f>SUM(H2:H5)</f>
+        <v>1971</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -1544,6 +1567,6 @@
     <row r="1001" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
-  <pageSetup orientation="landscape"/>
+  <pageSetup orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/data/Oficina_de_procuradora_de_mujeres/opmMedio.xlsx
+++ b/data/Oficina_de_procuradora_de_mujeres/opmMedio.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Oficina_de_procuradora_de_mujeres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7594442B-7C54-4078-8EBB-05A78EAA336F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF16FC4-CBBA-43DB-80FF-895A7CC57397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11424" yWindow="0" windowWidth="11712" windowHeight="13056" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1836" yWindow="1776" windowWidth="11424" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -454,7 +454,7 @@
         <v>2752</v>
       </c>
       <c r="H2" s="8">
-        <v>1447</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="3" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -506,7 +506,7 @@
         <v>255</v>
       </c>
       <c r="H4" s="8">
-        <v>123</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="1:8" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -532,7 +532,7 @@
         <v>654</v>
       </c>
       <c r="H5" s="8">
-        <v>397</v>
+        <v>446</v>
       </c>
     </row>
     <row r="6" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -564,8 +564,7 @@
         <v>3663</v>
       </c>
       <c r="H6">
-        <f>SUM(H2:H5)</f>
-        <v>1971</v>
+        <v>2310</v>
       </c>
     </row>
     <row r="7" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/data/Oficina_de_procuradora_de_mujeres/opmMedio.xlsx
+++ b/data/Oficina_de_procuradora_de_mujeres/opmMedio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gnper\Documents\ViolenciaGeneroPR\data\Oficina_de_procuradora_de_mujeres\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EF16FC4-CBBA-43DB-80FF-895A7CC57397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BA0674D-612C-4515-A8E7-C9DB465E0D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1836" yWindow="1776" windowWidth="11424" windowHeight="9420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10068" yWindow="2064" windowWidth="12132" windowHeight="9384" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -80,7 +80,7 @@
     <t>Personas atendidas (enero - diciembre 2025)</t>
   </si>
   <si>
-    <t>Personas atendidas (enero - julio 2026)</t>
+    <t>Personas atendidas (enero - agosto 2026)</t>
   </si>
 </sst>
 </file>
